--- a/output/details/2026-05-17/preprocessed_data.xlsx
+++ b/output/details/2026-05-17/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46159</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1107339684131949</v>
+        <v>-0.112667320190069</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1634877796764029</v>
+        <v>-0.1397130170480658</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1632601406927898</v>
+        <v>-0.1394381629145087</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1262785757713396</v>
+        <v>0.0001526650363508084</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001701545946909164</v>
+        <v>0.001700039515172292</v>
       </c>
       <c r="G2" t="n">
-        <v>1.893259022104339</v>
+        <v>2.462686609546489</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4465207737845152</v>
+        <v>-0.2667867817355726</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
